--- a/J859/source_data/J859_scenario_data_2015transition.xlsx
+++ b/J859/source_data/J859_scenario_data_2015transition.xlsx
@@ -1366,7 +1366,7 @@
         <v>45383</v>
       </c>
       <c r="B111" t="n">
-        <v>28.02</v>
+        <v>30.80962238992283</v>
       </c>
     </row>
     <row r="112">
@@ -1374,7 +1374,7 @@
         <v>45413</v>
       </c>
       <c r="B112" t="n">
-        <v>27.85132653061225</v>
+        <v>30.74924477984566</v>
       </c>
       <c r="C112" t="n">
         <v>-0.77</v>
@@ -1385,7 +1385,7 @@
         <v>45444</v>
       </c>
       <c r="B113" t="n">
-        <v>27.85132653061225</v>
+        <v>30.6888671697685</v>
       </c>
       <c r="C113" t="n">
         <v>-29.86</v>
@@ -1396,7 +1396,7 @@
         <v>45474</v>
       </c>
       <c r="B114" t="n">
-        <v>27.85132653061225</v>
+        <v>30.62848955969133</v>
       </c>
       <c r="C114" t="n">
         <v>-54.23</v>
@@ -1407,7 +1407,7 @@
         <v>45505</v>
       </c>
       <c r="B115" t="n">
-        <v>27.85132653061225</v>
+        <v>30.56811194961416</v>
       </c>
       <c r="C115" t="n">
         <v>-60.08</v>
@@ -1418,7 +1418,7 @@
         <v>45536</v>
       </c>
       <c r="B116" t="n">
-        <v>27.85132653061225</v>
+        <v>30.50773433953699</v>
       </c>
       <c r="C116" t="n">
         <v>-57.23</v>
@@ -1429,7 +1429,7 @@
         <v>45566</v>
       </c>
       <c r="B117" t="n">
-        <v>27.85132653061225</v>
+        <v>30.44735672945982</v>
       </c>
       <c r="C117" t="n">
         <v>-54.38</v>
@@ -1440,7 +1440,7 @@
         <v>45597</v>
       </c>
       <c r="B118" t="n">
-        <v>27.85132653061225</v>
+        <v>30.38697911938266</v>
       </c>
       <c r="C118" t="n">
         <v>-51.52999999999999</v>
@@ -1451,7 +1451,7 @@
         <v>45627</v>
       </c>
       <c r="B119" t="n">
-        <v>27.85132653061225</v>
+        <v>30.32660150930549</v>
       </c>
       <c r="C119" t="n">
         <v>-48.67999999999999</v>
@@ -1462,7 +1462,7 @@
         <v>45658</v>
       </c>
       <c r="B120" t="n">
-        <v>27.85132653061225</v>
+        <v>30.26622389922832</v>
       </c>
       <c r="C120" t="n">
         <v>-45.82999999999999</v>
@@ -1473,7 +1473,7 @@
         <v>45689</v>
       </c>
       <c r="B121" t="n">
-        <v>27.85132653061225</v>
+        <v>30.20584628915115</v>
       </c>
       <c r="C121" t="n">
         <v>-42.97999999999999</v>
@@ -1484,7 +1484,7 @@
         <v>45717</v>
       </c>
       <c r="B122" t="n">
-        <v>27.85132653061225</v>
+        <v>30.14546867907398</v>
       </c>
       <c r="C122" t="n">
         <v>-40.12999999999999</v>
@@ -1495,7 +1495,7 @@
         <v>45748</v>
       </c>
       <c r="B123" t="n">
-        <v>27.85132653061225</v>
+        <v>30.08509106899681</v>
       </c>
       <c r="C123" t="n">
         <v>-37.27999999999999</v>
@@ -1506,7 +1506,7 @@
         <v>45778</v>
       </c>
       <c r="B124" t="n">
-        <v>27.85132653061225</v>
+        <v>30.02471345891965</v>
       </c>
       <c r="C124" t="n">
         <v>-34.42999999999999</v>
@@ -1517,7 +1517,7 @@
         <v>45809</v>
       </c>
       <c r="B125" t="n">
-        <v>27.85132653061225</v>
+        <v>29.96433584884248</v>
       </c>
       <c r="C125" t="n">
         <v>-31.57999999999998</v>
@@ -1528,7 +1528,7 @@
         <v>45839</v>
       </c>
       <c r="B126" t="n">
-        <v>27.85132653061225</v>
+        <v>29.90395823876531</v>
       </c>
       <c r="C126" t="n">
         <v>-28.72999999999998</v>
@@ -1539,7 +1539,7 @@
         <v>45870</v>
       </c>
       <c r="B127" t="n">
-        <v>27.85132653061225</v>
+        <v>29.84358062868814</v>
       </c>
       <c r="C127" t="n">
         <v>-25.87999999999998</v>
@@ -1550,7 +1550,7 @@
         <v>45901</v>
       </c>
       <c r="B128" t="n">
-        <v>27.85132653061225</v>
+        <v>29.78320301861097</v>
       </c>
       <c r="C128" t="n">
         <v>-23.02999999999998</v>
@@ -1561,7 +1561,7 @@
         <v>45931</v>
       </c>
       <c r="B129" t="n">
-        <v>27.85132653061225</v>
+        <v>29.7228254085338</v>
       </c>
       <c r="C129" t="n">
         <v>-20.17999999999998</v>
@@ -1572,7 +1572,7 @@
         <v>45962</v>
       </c>
       <c r="B130" t="n">
-        <v>27.85132653061225</v>
+        <v>29.66244779845664</v>
       </c>
       <c r="C130" t="n">
         <v>-17.32999999999998</v>
@@ -1583,7 +1583,7 @@
         <v>45992</v>
       </c>
       <c r="B131" t="n">
-        <v>27.85132653061225</v>
+        <v>29.60207018837947</v>
       </c>
       <c r="C131" t="n">
         <v>-14.47999999999998</v>
@@ -1594,7 +1594,7 @@
         <v>46023</v>
       </c>
       <c r="B132" t="n">
-        <v>27.85132653061225</v>
+        <v>29.5416925783023</v>
       </c>
       <c r="C132" t="n">
         <v>-11.62999999999998</v>
@@ -1605,7 +1605,7 @@
         <v>46054</v>
       </c>
       <c r="B133" t="n">
-        <v>27.85132653061225</v>
+        <v>29.48131496822513</v>
       </c>
       <c r="C133" t="n">
         <v>-8.779999999999978</v>
@@ -1616,7 +1616,7 @@
         <v>46082</v>
       </c>
       <c r="B134" t="n">
-        <v>27.85132653061225</v>
+        <v>29.42093735814796</v>
       </c>
       <c r="C134" t="n">
         <v>-5.929999999999978</v>
@@ -1627,7 +1627,7 @@
         <v>46113</v>
       </c>
       <c r="B135" t="n">
-        <v>27.85132653061225</v>
+        <v>29.36055974807079</v>
       </c>
       <c r="C135" t="n">
         <v>-3.079999999999978</v>
@@ -1638,7 +1638,7 @@
         <v>46143</v>
       </c>
       <c r="B136" t="n">
-        <v>27.85132653061225</v>
+        <v>29.30018213799363</v>
       </c>
       <c r="C136" t="n">
         <v>-0.2299999999999782</v>
@@ -1649,7 +1649,7 @@
         <v>46174</v>
       </c>
       <c r="B137" t="n">
-        <v>27.85132653061225</v>
+        <v>29.23980452791646</v>
       </c>
       <c r="C137" t="n">
         <v>2.620000000000022</v>
@@ -1660,7 +1660,7 @@
         <v>46204</v>
       </c>
       <c r="B138" t="n">
-        <v>27.85132653061225</v>
+        <v>29.17942691783929</v>
       </c>
       <c r="C138" t="n">
         <v>3.55</v>
@@ -1671,7 +1671,7 @@
         <v>46235</v>
       </c>
       <c r="B139" t="n">
-        <v>27.85132653061225</v>
+        <v>29.11904930776212</v>
       </c>
       <c r="C139" t="n">
         <v>3.55</v>
@@ -1682,7 +1682,7 @@
         <v>46266</v>
       </c>
       <c r="B140" t="n">
-        <v>27.85132653061225</v>
+        <v>29.05867169768495</v>
       </c>
       <c r="C140" t="n">
         <v>3.55</v>
@@ -1693,7 +1693,7 @@
         <v>46296</v>
       </c>
       <c r="B141" t="n">
-        <v>27.85132653061225</v>
+        <v>28.99829408760779</v>
       </c>
       <c r="C141" t="n">
         <v>3.55</v>
@@ -1704,7 +1704,7 @@
         <v>46327</v>
       </c>
       <c r="B142" t="n">
-        <v>27.85132653061225</v>
+        <v>28.93791647753062</v>
       </c>
       <c r="C142" t="n">
         <v>3.55</v>
@@ -1715,7 +1715,7 @@
         <v>46357</v>
       </c>
       <c r="B143" t="n">
-        <v>27.85132653061225</v>
+        <v>28.87753886745345</v>
       </c>
       <c r="C143" t="n">
         <v>3.55</v>
@@ -1726,7 +1726,7 @@
         <v>46388</v>
       </c>
       <c r="B144" t="n">
-        <v>27.85132653061225</v>
+        <v>28.81716125737628</v>
       </c>
       <c r="C144" t="n">
         <v>3.55</v>
@@ -1737,7 +1737,7 @@
         <v>46419</v>
       </c>
       <c r="B145" t="n">
-        <v>27.85132653061225</v>
+        <v>28.75678364729911</v>
       </c>
       <c r="C145" t="n">
         <v>3.55</v>
@@ -1748,7 +1748,7 @@
         <v>46447</v>
       </c>
       <c r="B146" t="n">
-        <v>27.85132653061225</v>
+        <v>28.69640603722194</v>
       </c>
       <c r="C146" t="n">
         <v>3.55</v>
@@ -1759,7 +1759,7 @@
         <v>46478</v>
       </c>
       <c r="B147" t="n">
-        <v>27.85132653061225</v>
+        <v>28.63602842714478</v>
       </c>
       <c r="C147" t="n">
         <v>3.55</v>
@@ -1770,7 +1770,7 @@
         <v>46508</v>
       </c>
       <c r="B148" t="n">
-        <v>27.85132653061225</v>
+        <v>28.57565081706761</v>
       </c>
       <c r="C148" t="n">
         <v>3.55</v>
@@ -1781,7 +1781,7 @@
         <v>46539</v>
       </c>
       <c r="B149" t="n">
-        <v>27.85132653061225</v>
+        <v>28.51527320699044</v>
       </c>
       <c r="C149" t="n">
         <v>3.55</v>
@@ -1792,7 +1792,7 @@
         <v>46569</v>
       </c>
       <c r="B150" t="n">
-        <v>27.85132653061225</v>
+        <v>28.45489559691327</v>
       </c>
       <c r="C150" t="n">
         <v>3.55</v>
@@ -1803,7 +1803,7 @@
         <v>46600</v>
       </c>
       <c r="B151" t="n">
-        <v>27.85132653061225</v>
+        <v>28.3945179868361</v>
       </c>
       <c r="C151" t="n">
         <v>3.55</v>
@@ -1814,7 +1814,7 @@
         <v>46631</v>
       </c>
       <c r="B152" t="n">
-        <v>27.85132653061225</v>
+        <v>28.33414037675893</v>
       </c>
       <c r="C152" t="n">
         <v>3.55</v>
@@ -1825,7 +1825,7 @@
         <v>46661</v>
       </c>
       <c r="B153" t="n">
-        <v>27.85132653061225</v>
+        <v>28.27376276668177</v>
       </c>
       <c r="C153" t="n">
         <v>3.55</v>
@@ -1836,7 +1836,7 @@
         <v>46692</v>
       </c>
       <c r="B154" t="n">
-        <v>27.85132653061225</v>
+        <v>28.2133851566046</v>
       </c>
       <c r="C154" t="n">
         <v>3.55</v>
@@ -1847,7 +1847,7 @@
         <v>46722</v>
       </c>
       <c r="B155" t="n">
-        <v>27.85132653061225</v>
+        <v>28.15300754652743</v>
       </c>
       <c r="C155" t="n">
         <v>3.55</v>
@@ -1858,7 +1858,7 @@
         <v>46753</v>
       </c>
       <c r="B156" t="n">
-        <v>27.85132653061225</v>
+        <v>28.09262993645026</v>
       </c>
       <c r="C156" t="n">
         <v>3.55</v>
@@ -1869,7 +1869,7 @@
         <v>46784</v>
       </c>
       <c r="B157" t="n">
-        <v>27.85132653061225</v>
+        <v>28.03225232637309</v>
       </c>
       <c r="C157" t="n">
         <v>3.55</v>
@@ -1880,7 +1880,7 @@
         <v>46813</v>
       </c>
       <c r="B158" t="n">
-        <v>27.85132653061225</v>
+        <v>27.97187471629593</v>
       </c>
       <c r="C158" t="n">
         <v>3.55</v>
@@ -1891,7 +1891,7 @@
         <v>46844</v>
       </c>
       <c r="B159" t="n">
-        <v>27.85132653061225</v>
+        <v>27.91149710621876</v>
       </c>
       <c r="C159" t="n">
         <v>3.55</v>
